--- a/public/StructureDefinition-pghd-symptom.xlsx
+++ b/public/StructureDefinition-pghd-symptom.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T16:28:41-06:00</t>
+    <t>2026-09-10T16:32:51-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/public/StructureDefinition-pghd-symptom.xlsx
+++ b/public/StructureDefinition-pghd-symptom.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4290" uniqueCount="602">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4290" uniqueCount="603">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-20T16:07:18-05:00</t>
+    <t>2026-10-08T19:53:09-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -981,6 +981,9 @@
   </si>
   <si>
     <t>Observation.code.coding.system</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/uv/phr/CodeSystem/observation-pghd-codes</t>
   </si>
   <si>
     <t>Observation.code.coding:PGHDCodes.version</t>
@@ -6360,7 +6363,7 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>92</v>
@@ -6394,7 +6397,7 @@
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>82</v>
+        <v>312</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>82</v>
@@ -6471,10 +6474,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6591,10 +6594,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6711,10 +6714,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6831,10 +6834,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6953,13 +6956,13 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>301</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D40" t="s" s="2">
         <v>82</v>
@@ -7022,7 +7025,7 @@
       </c>
       <c r="Y40" s="2"/>
       <c r="Z40" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>82</v>
@@ -7075,7 +7078,7 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B41" t="s" s="2">
         <v>307</v>
@@ -7193,7 +7196,7 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>309</v>
@@ -7313,7 +7316,7 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>311</v>
@@ -7358,7 +7361,7 @@
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="S43" t="s" s="2">
         <v>82</v>
@@ -7435,10 +7438,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7555,10 +7558,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7675,10 +7678,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7795,10 +7798,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7917,10 +7920,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8039,10 +8042,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8065,19 +8068,19 @@
         <v>93</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -8126,7 +8129,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8141,19 +8144,19 @@
         <v>104</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>82</v>
@@ -8161,10 +8164,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8187,16 +8190,16 @@
         <v>93</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8246,7 +8249,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8270,10 +8273,10 @@
         <v>295</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>82</v>
@@ -8281,14 +8284,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -8307,19 +8310,19 @@
         <v>93</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -8368,7 +8371,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8383,19 +8386,19 @@
         <v>104</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>82</v>
@@ -8403,14 +8406,14 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8429,19 +8432,19 @@
         <v>93</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -8490,7 +8493,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8505,19 +8508,19 @@
         <v>104</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>82</v>
@@ -8525,10 +8528,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8551,16 +8554,16 @@
         <v>93</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8610,7 +8613,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8631,13 +8634,13 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>82</v>
@@ -8645,10 +8648,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8671,17 +8674,17 @@
         <v>93</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -8730,7 +8733,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8745,19 +8748,19 @@
         <v>104</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>82</v>
@@ -8765,10 +8768,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8794,16 +8797,16 @@
         <v>190</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -8852,7 +8855,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8861,7 +8864,7 @@
         <v>92</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>104</v>
@@ -8870,27 +8873,27 @@
         <v>82</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9005,10 +9008,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9125,10 +9128,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9245,13 +9248,13 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="B59" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="B59" t="s" s="2">
-        <v>399</v>
-      </c>
       <c r="C59" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D59" t="s" s="2">
         <v>82</v>
@@ -9314,7 +9317,7 @@
       </c>
       <c r="Y59" s="2"/>
       <c r="Z59" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>82</v>
@@ -9367,10 +9370,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9485,10 +9488,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9605,10 +9608,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9650,7 +9653,7 @@
       </c>
       <c r="Q62" s="2"/>
       <c r="R62" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="S62" t="s" s="2">
         <v>82</v>
@@ -9727,10 +9730,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9847,10 +9850,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9967,10 +9970,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10087,10 +10090,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10209,13 +10212,13 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D67" t="s" s="2">
         <v>82</v>
@@ -10278,7 +10281,7 @@
       </c>
       <c r="Y67" s="2"/>
       <c r="Z67" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>82</v>
@@ -10331,10 +10334,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10449,10 +10452,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10569,10 +10572,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10614,7 +10617,7 @@
       </c>
       <c r="Q70" s="2"/>
       <c r="R70" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="S70" t="s" s="2">
         <v>82</v>
@@ -10691,10 +10694,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10811,10 +10814,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10931,10 +10934,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11051,10 +11054,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11173,13 +11176,13 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D75" t="s" s="2">
         <v>82</v>
@@ -11242,7 +11245,7 @@
       </c>
       <c r="Y75" s="2"/>
       <c r="Z75" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>82</v>
@@ -11295,10 +11298,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11413,10 +11416,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11533,10 +11536,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11578,7 +11581,7 @@
       </c>
       <c r="Q78" s="2"/>
       <c r="R78" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="S78" t="s" s="2">
         <v>82</v>
@@ -11655,10 +11658,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11775,10 +11778,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11895,10 +11898,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12015,10 +12018,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12137,10 +12140,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12259,10 +12262,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12288,16 +12291,16 @@
         <v>190</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>82</v>
@@ -12322,13 +12325,13 @@
         <v>82</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>82</v>
@@ -12346,7 +12349,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12355,7 +12358,7 @@
         <v>92</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AJ84" t="s" s="2">
         <v>104</v>
@@ -12370,7 +12373,7 @@
         <v>135</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>82</v>
@@ -12381,14 +12384,14 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -12410,16 +12413,16 @@
         <v>190</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>82</v>
@@ -12444,13 +12447,13 @@
         <v>82</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>82</v>
@@ -12468,7 +12471,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12486,27 +12489,27 @@
         <v>82</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12529,19 +12532,19 @@
         <v>82</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>82</v>
@@ -12590,7 +12593,7 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12611,10 +12614,10 @@
         <v>82</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>82</v>
@@ -12625,10 +12628,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12654,13 +12657,13 @@
         <v>190</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -12689,10 +12692,10 @@
         <v>290</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>82</v>
@@ -12710,7 +12713,7 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12728,27 +12731,27 @@
         <v>82</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP87" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12774,16 +12777,16 @@
         <v>190</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>82</v>
@@ -12811,10 +12814,10 @@
         <v>290</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>82</v>
@@ -12832,7 +12835,7 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -12853,10 +12856,10 @@
         <v>82</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>82</v>
@@ -12867,10 +12870,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12893,16 +12896,16 @@
         <v>82</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -12952,7 +12955,7 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -12970,27 +12973,27 @@
         <v>82</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13013,16 +13016,16 @@
         <v>82</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -13072,7 +13075,7 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -13090,27 +13093,27 @@
         <v>82</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP90" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13133,19 +13136,19 @@
         <v>82</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>82</v>
@@ -13194,7 +13197,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13206,7 +13209,7 @@
         <v>82</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>82</v>
@@ -13215,10 +13218,10 @@
         <v>82</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>82</v>
@@ -13229,10 +13232,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13347,10 +13350,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13467,14 +13470,14 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
@@ -13496,10 +13499,10 @@
         <v>138</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="N94" t="s" s="2">
         <v>141</v>
@@ -13554,7 +13557,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13589,10 +13592,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13615,13 +13618,13 @@
         <v>82</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -13672,7 +13675,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -13681,7 +13684,7 @@
         <v>92</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AJ95" t="s" s="2">
         <v>104</v>
@@ -13693,10 +13696,10 @@
         <v>82</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>82</v>
@@ -13707,10 +13710,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13733,13 +13736,13 @@
         <v>82</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -13790,7 +13793,7 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -13799,7 +13802,7 @@
         <v>92</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AJ96" t="s" s="2">
         <v>104</v>
@@ -13811,10 +13814,10 @@
         <v>82</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>82</v>
@@ -13825,10 +13828,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13854,16 +13857,16 @@
         <v>190</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>82</v>
@@ -13891,10 +13894,10 @@
         <v>116</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>82</v>
@@ -13912,7 +13915,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -13930,13 +13933,13 @@
         <v>82</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>82</v>
@@ -13947,10 +13950,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13976,16 +13979,16 @@
         <v>190</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>82</v>
@@ -14013,10 +14016,10 @@
         <v>290</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>82</v>
@@ -14034,7 +14037,7 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -14052,13 +14055,13 @@
         <v>82</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>82</v>
@@ -14069,10 +14072,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14095,17 +14098,17 @@
         <v>82</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>82</v>
@@ -14154,7 +14157,7 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -14178,7 +14181,7 @@
         <v>82</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>82</v>
@@ -14189,10 +14192,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14218,10 +14221,10 @@
         <v>205</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -14272,7 +14275,7 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14293,10 +14296,10 @@
         <v>82</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>82</v>
@@ -14307,10 +14310,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14333,16 +14336,16 @@
         <v>93</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -14392,7 +14395,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14413,10 +14416,10 @@
         <v>82</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>82</v>
@@ -14427,10 +14430,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14453,16 +14456,16 @@
         <v>93</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -14512,7 +14515,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14533,10 +14536,10 @@
         <v>82</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>82</v>
@@ -14547,10 +14550,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14573,19 +14576,19 @@
         <v>93</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>82</v>
@@ -14634,7 +14637,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -14655,10 +14658,10 @@
         <v>82</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>82</v>
@@ -14669,10 +14672,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14787,10 +14790,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14907,14 +14910,14 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -14936,10 +14939,10 @@
         <v>138</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="N106" t="s" s="2">
         <v>141</v>
@@ -14994,7 +14997,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15029,10 +15032,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15058,13 +15061,13 @@
         <v>190</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="O107" t="s" s="2">
         <v>289</v>
@@ -15116,7 +15119,7 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>92</v>
@@ -15134,7 +15137,7 @@
         <v>82</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>295</v>
@@ -15151,10 +15154,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15177,19 +15180,19 @@
         <v>93</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>82</v>
@@ -15238,7 +15241,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15256,27 +15259,27 @@
         <v>82</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP108" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15302,16 +15305,16 @@
         <v>190</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>82</v>
@@ -15336,13 +15339,13 @@
         <v>82</v>
       </c>
       <c r="X109" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="Y109" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="Z109" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>82</v>
@@ -15360,7 +15363,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15369,7 +15372,7 @@
         <v>92</v>
       </c>
       <c r="AI109" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AJ109" t="s" s="2">
         <v>104</v>
@@ -15384,7 +15387,7 @@
         <v>135</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>82</v>
@@ -15395,14 +15398,14 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
@@ -15424,16 +15427,16 @@
         <v>190</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>82</v>
@@ -15458,13 +15461,13 @@
         <v>82</v>
       </c>
       <c r="X110" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="Z110" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>82</v>
@@ -15482,7 +15485,7 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -15500,27 +15503,27 @@
         <v>82</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP110" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15546,16 +15549,16 @@
         <v>83</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>82</v>
@@ -15604,7 +15607,7 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -15625,10 +15628,10 @@
         <v>82</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>82</v>
